--- a/output/Tables/Scenarios/HIA_add_scenarios.xlsx
+++ b/output/Tables/Scenarios/HIA_add_scenarios.xlsx
@@ -423,40 +423,40 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>749171.939</v>
+        <v>600709.0600000001</v>
       </c>
       <c r="B2">
-        <v>739181.1360000001</v>
+        <v>594047.197</v>
       </c>
       <c r="C2">
-        <v>759107.7250000001</v>
+        <v>607287.8230000001</v>
       </c>
       <c r="D2">
-        <v>1513284.632</v>
+        <v>1411133.246</v>
       </c>
       <c r="E2">
-        <v>1497410.51</v>
+        <v>1399036.169</v>
       </c>
       <c r="F2">
-        <v>1529218.179</v>
+        <v>1423393.406</v>
       </c>
       <c r="G2">
-        <v>9585513523.317001</v>
+        <v>7000545630.594</v>
       </c>
       <c r="H2">
-        <v>9431146725.460001</v>
+        <v>6898174163.748999</v>
       </c>
       <c r="I2">
-        <v>9741544352.556999</v>
+        <v>7103471935.424</v>
       </c>
       <c r="J2">
-        <v>201268309936.555</v>
+        <v>187688257013.653</v>
       </c>
       <c r="K2">
-        <v>199147675007.879</v>
+        <v>186058734708.614</v>
       </c>
       <c r="L2">
-        <v>203379184933.759</v>
+        <v>189309618960.638</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -466,40 +466,40 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>68790.304</v>
+        <v>71117.86900000001</v>
       </c>
       <c r="B3">
-        <v>66630.64900000003</v>
+        <v>68966.83799999999</v>
       </c>
       <c r="C3">
-        <v>71050.75599999999</v>
+        <v>73321.378</v>
       </c>
       <c r="D3">
-        <v>158011.2120000001</v>
+        <v>165780.9589999999</v>
       </c>
       <c r="E3">
-        <v>154397.213</v>
+        <v>162413.7350000001</v>
       </c>
       <c r="F3">
-        <v>161797.5749999998</v>
+        <v>169340.2340000001</v>
       </c>
       <c r="G3">
-        <v>865035502.4180012</v>
+        <v>779848077.7459998</v>
       </c>
       <c r="H3">
-        <v>836710268.915</v>
+        <v>756385181.586</v>
       </c>
       <c r="I3">
-        <v>895045293.5889997</v>
+        <v>804909002.21</v>
       </c>
       <c r="J3">
-        <v>21014333824.20601</v>
+        <v>22050708515.077</v>
       </c>
       <c r="K3">
-        <v>20542800374.77501</v>
+        <v>21607393554.04402</v>
       </c>
       <c r="L3">
-        <v>21522856907.521</v>
+        <v>22521733383.123</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -509,40 +509,40 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>193118.2689999999</v>
+        <v>177955.527</v>
       </c>
       <c r="B4">
-        <v>188767.9449999999</v>
+        <v>174034.137</v>
       </c>
       <c r="C4">
-        <v>197282.7129999999</v>
+        <v>181855.3520000001</v>
       </c>
       <c r="D4">
-        <v>596366.322</v>
+        <v>622685.9099999995</v>
       </c>
       <c r="E4">
-        <v>585981.6339999997</v>
+        <v>610945.691</v>
       </c>
       <c r="F4">
-        <v>606408.748</v>
+        <v>634442.517</v>
       </c>
       <c r="G4">
-        <v>2305725776.639</v>
+        <v>2172652064.846002</v>
       </c>
       <c r="H4">
-        <v>2266443421.789999</v>
+        <v>2125068158.237999</v>
       </c>
       <c r="I4">
-        <v>2343324287.537999</v>
+        <v>2219933937.351001</v>
       </c>
       <c r="J4">
-        <v>79318557723.62701</v>
+        <v>82819765860.93596</v>
       </c>
       <c r="K4">
-        <v>77942435556.5591</v>
+        <v>81248899348.34198</v>
       </c>
       <c r="L4">
-        <v>80660270590.14401</v>
+        <v>84382915775.47302</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
